--- a/newProject/data_preparation/input_data/ExampleExcel.xlsx
+++ b/newProject/data_preparation/input_data/ExampleExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/i553815/lerning/bibliographic_analysis/newProject/data_preparation/input_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067D47D4-0EEF-E147-B32C-E289497E3A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEE82D2-5C20-0042-9F6E-EA6C40E891E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20500" xr2:uid="{9861EEE3-01A7-DF47-890C-7048CC74371C}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20480" xr2:uid="{9861EEE3-01A7-DF47-890C-7048CC74371C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>Document Type</t>
   </si>
@@ -514,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DB183FA-A8C2-F14F-A81C-90A8247F06EC}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="9" max="9" width="10.83203125" customWidth="1"/>
@@ -610,6 +610,32 @@
         <v>16</v>
       </c>
     </row>
+    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
